--- a/results/attrition/tables_data/attrition_intensive.xlsx
+++ b/results/attrition/tables_data/attrition_intensive.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -399,20 +399,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dummy_attrition</t>
+          <t>overall_blocked</t>
         </is>
       </c>
       <c r="C2">
-        <v>0.01012510602205259</v>
+        <v>0.005619168787107718</v>
       </c>
       <c r="D2">
-        <v>0.003993148762772188</v>
+        <v>0.00379020907736581</v>
       </c>
       <c r="E2">
-        <v>0.002435956517213146</v>
+        <v>0.001652661208967884</v>
       </c>
       <c r="F2">
-        <v>0.1011606027146134</v>
+        <v>0.02182513070456026</v>
       </c>
       <c r="G2">
         <v>100690</v>
@@ -426,20 +426,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>overall_blocked</t>
+          <t>dummy_both</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.005619168787107718</v>
+        <v>0.01574427480916031</v>
       </c>
       <c r="D3">
-        <v>0.00379020907736581</v>
+        <v>0.007783357840130022</v>
       </c>
       <c r="E3">
-        <v>0.001652661208967884</v>
+        <v>0.00364219775404082</v>
       </c>
       <c r="F3">
-        <v>0.02182513070456026</v>
+        <v>0.032598410564459</v>
       </c>
       <c r="G3">
         <v>100690</v>
@@ -448,28 +448,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b1</t>
+          <t>b2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dummy_both</t>
+          <t>dummy_attrition</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.01574427480916031</v>
+        <v>0.1522568340750159</v>
       </c>
       <c r="D4">
-        <v>0.007783357840130022</v>
+        <v>-0.02477226904139536</v>
       </c>
       <c r="E4">
-        <v>0.00364219775404082</v>
+        <v>0.01546052045452475</v>
       </c>
       <c r="F4">
-        <v>0.032598410564459</v>
+        <v>0.1090910424572755</v>
       </c>
       <c r="G4">
-        <v>100690</v>
+        <v>45376</v>
       </c>
     </row>
     <row r="5">
@@ -480,20 +480,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dummy_attrition</t>
+          <t>overall_blocked</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.1522568340750159</v>
+        <v>0.09917355371900827</v>
       </c>
       <c r="D5">
-        <v>-0.02477226904139536</v>
+        <v>-0.01419877904367099</v>
       </c>
       <c r="E5">
-        <v>0.01546052045452475</v>
+        <v>0.006949089101812978</v>
       </c>
       <c r="F5">
-        <v>0.1090910424572755</v>
+        <v>0.0410269455710857</v>
       </c>
       <c r="G5">
         <v>45376</v>
@@ -507,131 +507,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>overall_blocked</t>
+          <t>dummy_both</t>
         </is>
       </c>
       <c r="C6">
-        <v>0.09917355371900827</v>
+        <v>0.2514303877940242</v>
       </c>
       <c r="D6">
-        <v>-0.01419877904367099</v>
+        <v>-0.03897104808501604</v>
       </c>
       <c r="E6">
-        <v>0.006949089101812978</v>
+        <v>0.02015434298296113</v>
       </c>
       <c r="F6">
-        <v>0.0410269455710857</v>
+        <v>0.05315860020704953</v>
       </c>
       <c r="G6">
         <v>45376</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dummy_both</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.2514303877940242</v>
-      </c>
-      <c r="D7">
-        <v>-0.03897104808501604</v>
-      </c>
-      <c r="E7">
-        <v>0.02015434298296113</v>
-      </c>
-      <c r="F7">
-        <v>0.05315860020704953</v>
-      </c>
-      <c r="G7">
-        <v>45376</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>dummy_attrition</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.04567498807441565</v>
-      </c>
-      <c r="D8">
-        <v>-0.005190436970841736</v>
-      </c>
-      <c r="E8">
-        <v>0.006526262898521806</v>
-      </c>
-      <c r="F8">
-        <v>0.4264300947435821</v>
-      </c>
-      <c r="G8">
-        <v>146066</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>overall_blocked</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.02901892192717443</v>
-      </c>
-      <c r="D9">
-        <v>8.946135947991918e-05</v>
-      </c>
-      <c r="E9">
-        <v>0.003272689813107492</v>
-      </c>
-      <c r="F9">
-        <v>0.9781919604605686</v>
-      </c>
-      <c r="G9">
-        <v>146066</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dummy_both</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.07469391000159008</v>
-      </c>
-      <c r="D10">
-        <v>-0.00510097561142417</v>
-      </c>
-      <c r="E10">
-        <v>0.006495402744238651</v>
-      </c>
-      <c r="F10">
-        <v>0.4322654374535904</v>
-      </c>
-      <c r="G10">
-        <v>146066</v>
       </c>
     </row>
   </sheetData>
